--- a/大秘境分数行情_至暗之夜第一赛季.xlsx
+++ b/大秘境分数行情_至暗之夜第一赛季.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ext.ahs.lvxingz1/note/WowDailyReport/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C30FF7A3-7792-F94A-AB25-0700D4BCC749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35780429-B149-3645-AA71-3271032645EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="2080" windowWidth="19920" windowHeight="15560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="120" yWindow="2080" windowWidth="16600" windowHeight="15560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="每日数据" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="71">
   <si>
     <t>日期</t>
   </si>
@@ -240,6 +240,10 @@
   </si>
   <si>
     <t>距离结束(周)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绿绿月光-H奶僧</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -640,7 +644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BF5"/>
+  <dimension ref="A1:BF6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -1541,6 +1545,182 @@
         <v>4208.3</v>
       </c>
     </row>
+    <row r="6" spans="1:58">
+      <c r="A6" s="3">
+        <v>20260720</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="3">
+        <v>17</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="3">
+        <v>4420.3</v>
+      </c>
+      <c r="F6" s="3">
+        <v>4246.51</v>
+      </c>
+      <c r="G6" s="3">
+        <v>3985.21</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I6" s="3">
+        <v>24</v>
+      </c>
+      <c r="J6" s="3">
+        <v>25</v>
+      </c>
+      <c r="K6" s="3">
+        <v>24</v>
+      </c>
+      <c r="L6" s="3">
+        <v>25</v>
+      </c>
+      <c r="M6" s="3">
+        <v>25</v>
+      </c>
+      <c r="N6" s="3">
+        <v>24</v>
+      </c>
+      <c r="O6" s="3">
+        <v>24</v>
+      </c>
+      <c r="P6" s="3">
+        <v>25</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>170</v>
+      </c>
+      <c r="R6" s="3">
+        <v>2430</v>
+      </c>
+      <c r="S6" s="4">
+        <v>4173.5</v>
+      </c>
+      <c r="T6" s="4">
+        <v>4250.3999999999996</v>
+      </c>
+      <c r="U6" s="4">
+        <v>4419.3999999999996</v>
+      </c>
+      <c r="V6" s="3">
+        <v>4419.1000000000004</v>
+      </c>
+      <c r="W6" s="3">
+        <v>4295.2</v>
+      </c>
+      <c r="X6" s="3">
+        <v>4164.3999999999996</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>4247</v>
+      </c>
+      <c r="Z6" s="3">
+        <v>4344.1000000000004</v>
+      </c>
+      <c r="AA6" s="3">
+        <v>4419.3999999999996</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>4137.5</v>
+      </c>
+      <c r="AC6" s="3">
+        <v>4418.7</v>
+      </c>
+      <c r="AD6" s="3">
+        <v>4033.2</v>
+      </c>
+      <c r="AE6" s="3">
+        <v>4280.2</v>
+      </c>
+      <c r="AF6" s="3">
+        <v>4359.3</v>
+      </c>
+      <c r="AG6" s="3">
+        <v>4219.6000000000004</v>
+      </c>
+      <c r="AH6" s="3">
+        <v>4253.8999999999996</v>
+      </c>
+      <c r="AI6" s="3">
+        <v>4254.3</v>
+      </c>
+      <c r="AJ6" s="3">
+        <v>4152.1000000000004</v>
+      </c>
+      <c r="AK6" s="3">
+        <v>4352.6000000000004</v>
+      </c>
+      <c r="AL6" s="3">
+        <v>4350.1000000000004</v>
+      </c>
+      <c r="AM6" s="3">
+        <v>4420.3</v>
+      </c>
+      <c r="AN6" s="3">
+        <v>4279.7</v>
+      </c>
+      <c r="AO6" s="3">
+        <v>4252.5</v>
+      </c>
+      <c r="AP6" s="3">
+        <v>4136.1000000000004</v>
+      </c>
+      <c r="AQ6" s="3">
+        <v>4350.1000000000004</v>
+      </c>
+      <c r="AR6" s="3">
+        <v>4371.8</v>
+      </c>
+      <c r="AS6" s="3">
+        <v>4146.3</v>
+      </c>
+      <c r="AT6" s="3">
+        <v>4338.5</v>
+      </c>
+      <c r="AU6" s="3">
+        <v>4331.2</v>
+      </c>
+      <c r="AV6" s="3">
+        <v>4334.1000000000004</v>
+      </c>
+      <c r="AW6" s="3">
+        <v>4295.2</v>
+      </c>
+      <c r="AX6" s="3">
+        <v>4313.1000000000004</v>
+      </c>
+      <c r="AY6" s="3">
+        <v>4312.8999999999996</v>
+      </c>
+      <c r="AZ6" s="3">
+        <v>4350.1000000000004</v>
+      </c>
+      <c r="BA6" s="3">
+        <v>4101.7</v>
+      </c>
+      <c r="BB6" s="3">
+        <v>4305.8999999999996</v>
+      </c>
+      <c r="BC6" s="3">
+        <v>4252.1000000000004</v>
+      </c>
+      <c r="BD6" s="3">
+        <v>4349.5</v>
+      </c>
+      <c r="BE6" s="3">
+        <v>4261.3999999999996</v>
+      </c>
+      <c r="BF6" s="3">
+        <v>4208.3</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/大秘境分数行情_至暗之夜第一赛季.xlsx
+++ b/大秘境分数行情_至暗之夜第一赛季.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ext.ahs.lvxingz1/note/WowDailyReport/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35780429-B149-3645-AA71-3271032645EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06107585-635A-CC48-B670-0D7D3ED075E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="2080" windowWidth="16600" windowHeight="15560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="120" yWindow="2080" windowWidth="26960" windowHeight="15560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="每日数据" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="69">
   <si>
     <t>日期</t>
   </si>
@@ -211,22 +211,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>T酒仙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>H奶萨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>D武器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>D惩戒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>最高铁人数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -244,6 +228,14 @@
   </si>
   <si>
     <t>绿绿月光-H奶僧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">4449.1	</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zacdruid-T熊T,Titiquemonk-H奶僧,Nzangellips-D噬灭,Myzouth-D邪DK,Nikovoker-D增辉</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -644,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BF6"/>
+  <dimension ref="A1:BF7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -676,7 +668,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>3</v>
@@ -715,10 +707,10 @@
         <v>8</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="R1" s="7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="S1" s="3" t="s">
         <v>50</v>
@@ -852,7 +844,7 @@
         <v>16</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E2" s="3">
         <v>4412</v>
@@ -1028,7 +1020,7 @@
         <v>16</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>60</v>
@@ -1204,7 +1196,7 @@
         <v>17</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>60</v>
@@ -1380,7 +1372,7 @@
         <v>17</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>60</v>
@@ -1556,7 +1548,7 @@
         <v>17</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E6" s="3">
         <v>4420.3</v>
@@ -1568,7 +1560,7 @@
         <v>3985.21</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I6" s="3">
         <v>24</v>
@@ -1598,7 +1590,7 @@
         <v>170</v>
       </c>
       <c r="R6" s="3">
-        <v>2430</v>
+        <v>1750</v>
       </c>
       <c r="S6" s="4">
         <v>4173.5</v>
@@ -1719,6 +1711,182 @@
       </c>
       <c r="BF6" s="3">
         <v>4208.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:58">
+      <c r="A7" s="3">
+        <v>20260727</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="3">
+        <v>18</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F7" s="3">
+        <v>4251.74</v>
+      </c>
+      <c r="G7" s="3">
+        <v>4008.83</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I7" s="3">
+        <v>24</v>
+      </c>
+      <c r="J7" s="3">
+        <v>25</v>
+      </c>
+      <c r="K7" s="3">
+        <v>24</v>
+      </c>
+      <c r="L7" s="3">
+        <v>25</v>
+      </c>
+      <c r="M7" s="3">
+        <v>25</v>
+      </c>
+      <c r="N7" s="3">
+        <v>24</v>
+      </c>
+      <c r="O7" s="3">
+        <v>25</v>
+      </c>
+      <c r="P7" s="3">
+        <v>25</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>190</v>
+      </c>
+      <c r="R7" s="3">
+        <v>2058</v>
+      </c>
+      <c r="S7" s="4">
+        <v>4187</v>
+      </c>
+      <c r="T7" s="4">
+        <v>4250.3999999999996</v>
+      </c>
+      <c r="U7" s="4">
+        <v>4449.1000000000004</v>
+      </c>
+      <c r="V7" s="4">
+        <v>4449.1000000000004</v>
+      </c>
+      <c r="W7" s="3">
+        <v>4296.2</v>
+      </c>
+      <c r="X7" s="3">
+        <v>4177.7</v>
+      </c>
+      <c r="Y7" s="3">
+        <v>4277.3999999999996</v>
+      </c>
+      <c r="Z7" s="4">
+        <v>4362.3999999999996</v>
+      </c>
+      <c r="AA7" s="4">
+        <v>4449.1000000000004</v>
+      </c>
+      <c r="AB7" s="3">
+        <v>4137.5</v>
+      </c>
+      <c r="AC7" s="4">
+        <v>4449.1000000000004</v>
+      </c>
+      <c r="AD7" s="3">
+        <v>4047.6</v>
+      </c>
+      <c r="AE7" s="3">
+        <v>4295.7</v>
+      </c>
+      <c r="AF7" s="3">
+        <v>4359.3</v>
+      </c>
+      <c r="AG7" s="3">
+        <v>4219.6000000000004</v>
+      </c>
+      <c r="AH7" s="3">
+        <v>4311.3</v>
+      </c>
+      <c r="AI7" s="3">
+        <v>4254.3</v>
+      </c>
+      <c r="AJ7" s="3">
+        <v>4214.5</v>
+      </c>
+      <c r="AK7" s="3">
+        <v>4360.1000000000004</v>
+      </c>
+      <c r="AL7" s="3">
+        <v>4364.5</v>
+      </c>
+      <c r="AM7" s="3">
+        <v>4449.1000000000004</v>
+      </c>
+      <c r="AN7" s="3">
+        <v>4292.5</v>
+      </c>
+      <c r="AO7" s="3">
+        <v>4252.5</v>
+      </c>
+      <c r="AP7" s="3">
+        <v>4206.3999999999996</v>
+      </c>
+      <c r="AQ7" s="3">
+        <v>4363.8999999999996</v>
+      </c>
+      <c r="AR7" s="3">
+        <v>4373.3</v>
+      </c>
+      <c r="AS7" s="3">
+        <v>4146.8</v>
+      </c>
+      <c r="AT7" s="3">
+        <v>4352.8999999999996</v>
+      </c>
+      <c r="AU7" s="3">
+        <v>4344.6000000000004</v>
+      </c>
+      <c r="AV7" s="3">
+        <v>4350.7</v>
+      </c>
+      <c r="AW7" s="3">
+        <v>4295.2</v>
+      </c>
+      <c r="AX7" s="3">
+        <v>4313.1000000000004</v>
+      </c>
+      <c r="AY7" s="3">
+        <v>4326.3</v>
+      </c>
+      <c r="AZ7" s="3">
+        <v>4364.7</v>
+      </c>
+      <c r="BA7" s="3">
+        <v>4101.7</v>
+      </c>
+      <c r="BB7" s="3">
+        <v>4320.1000000000004</v>
+      </c>
+      <c r="BC7" s="3">
+        <v>4283</v>
+      </c>
+      <c r="BD7" s="3">
+        <v>4369</v>
+      </c>
+      <c r="BE7" s="3">
+        <v>4311.8999999999996</v>
+      </c>
+      <c r="BF7" s="3">
+        <v>4232.7</v>
       </c>
     </row>
   </sheetData>
@@ -1730,7 +1898,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1765,23 +1933,6 @@
       </c>
       <c r="E2" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E3" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/大秘境分数行情_至暗之夜第一赛季.xlsx
+++ b/大秘境分数行情_至暗之夜第一赛季.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ext.ahs.lvxingz1/note/WowDailyReport/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E16A1234-55C0-7845-9A42-103FCE093958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB813278-CAB6-3747-BADF-ACBCDFB001C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="2080" windowWidth="26960" windowHeight="15560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="每日数据" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="74">
   <si>
     <t>日期</t>
   </si>
@@ -633,7 +633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BI9"/>
+  <dimension ref="A1:BI10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -651,8 +651,8 @@
     <col min="14" max="14" width="7.5" style="3" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="25" width="8.83203125" style="3" customWidth="1"/>
-    <col min="26" max="16384" width="8.83203125" style="3"/>
+    <col min="19" max="26" width="8.83203125" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:61" s="2" customFormat="1">
@@ -2228,6 +2228,191 @@
       </c>
       <c r="BI9">
         <v>16446</v>
+      </c>
+    </row>
+    <row r="10" spans="1:61">
+      <c r="A10">
+        <v>20260731</v>
+      </c>
+      <c r="B10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="3">
+        <v>19</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>4449.3999999999996</v>
+      </c>
+      <c r="F10">
+        <v>4254.08</v>
+      </c>
+      <c r="G10">
+        <v>4011.89</v>
+      </c>
+      <c r="H10" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10">
+        <v>24</v>
+      </c>
+      <c r="J10">
+        <v>25</v>
+      </c>
+      <c r="K10">
+        <v>24</v>
+      </c>
+      <c r="L10">
+        <v>25</v>
+      </c>
+      <c r="M10">
+        <v>25</v>
+      </c>
+      <c r="N10">
+        <v>24</v>
+      </c>
+      <c r="O10">
+        <v>25</v>
+      </c>
+      <c r="P10">
+        <v>25</v>
+      </c>
+      <c r="Q10">
+        <v>4216.7</v>
+      </c>
+      <c r="R10">
+        <v>4250.3999999999996</v>
+      </c>
+      <c r="S10">
+        <v>4449.3999999999996</v>
+      </c>
+      <c r="T10">
+        <v>4449.2</v>
+      </c>
+      <c r="U10">
+        <v>4304</v>
+      </c>
+      <c r="V10">
+        <v>4211.6000000000004</v>
+      </c>
+      <c r="W10">
+        <v>4277.3999999999996</v>
+      </c>
+      <c r="X10">
+        <v>4379</v>
+      </c>
+      <c r="Y10">
+        <v>4449.1000000000004</v>
+      </c>
+      <c r="Z10">
+        <v>4137.5</v>
+      </c>
+      <c r="AA10">
+        <v>4449.3999999999996</v>
+      </c>
+      <c r="AB10">
+        <v>4061.2</v>
+      </c>
+      <c r="AC10">
+        <v>4295.7</v>
+      </c>
+      <c r="AD10">
+        <v>4374.5</v>
+      </c>
+      <c r="AE10">
+        <v>4219.6000000000004</v>
+      </c>
+      <c r="AF10">
+        <v>4315.6000000000004</v>
+      </c>
+      <c r="AG10">
+        <v>4254.3</v>
+      </c>
+      <c r="AH10">
+        <v>4225.6000000000004</v>
+      </c>
+      <c r="AI10">
+        <v>4361.3</v>
+      </c>
+      <c r="AJ10">
+        <v>4379</v>
+      </c>
+      <c r="AK10">
+        <v>4449.3999999999996</v>
+      </c>
+      <c r="AL10">
+        <v>4292.5</v>
+      </c>
+      <c r="AM10">
+        <v>4266.5</v>
+      </c>
+      <c r="AN10">
+        <v>4206.3999999999996</v>
+      </c>
+      <c r="AO10">
+        <v>4372.2</v>
+      </c>
+      <c r="AP10">
+        <v>4373.3</v>
+      </c>
+      <c r="AQ10">
+        <v>4176.7</v>
+      </c>
+      <c r="AR10">
+        <v>4365.7</v>
+      </c>
+      <c r="AS10">
+        <v>4346.6000000000004</v>
+      </c>
+      <c r="AT10">
+        <v>4365.1000000000004</v>
+      </c>
+      <c r="AU10">
+        <v>4295.2</v>
+      </c>
+      <c r="AV10">
+        <v>4326.5</v>
+      </c>
+      <c r="AW10">
+        <v>4341.2</v>
+      </c>
+      <c r="AX10">
+        <v>4379</v>
+      </c>
+      <c r="AY10">
+        <v>4101.7</v>
+      </c>
+      <c r="AZ10">
+        <v>4347.3</v>
+      </c>
+      <c r="BA10">
+        <v>4327.8</v>
+      </c>
+      <c r="BB10">
+        <v>4379</v>
+      </c>
+      <c r="BC10">
+        <v>4325.1000000000004</v>
+      </c>
+      <c r="BD10">
+        <v>4236.3</v>
+      </c>
+      <c r="BE10">
+        <v>4019.01</v>
+      </c>
+      <c r="BF10">
+        <v>4256.62</v>
+      </c>
+      <c r="BG10">
+        <v>1647865</v>
+      </c>
+      <c r="BH10">
+        <v>1648</v>
+      </c>
+      <c r="BI10">
+        <v>16481</v>
       </c>
     </row>
   </sheetData>

--- a/大秘境分数行情_至暗之夜第一赛季.xlsx
+++ b/大秘境分数行情_至暗之夜第一赛季.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ext.ahs.lvxingz1/note/WowDailyReport/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6FF480-95A1-3B47-BFB7-61024AB9A398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6443EE81-0F2C-1745-9A21-27DEAE8B8F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="74">
   <si>
     <t>日期</t>
   </si>
@@ -633,7 +633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BI10"/>
+  <dimension ref="A1:BI9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -2230,191 +2230,6 @@
         <v>16446</v>
       </c>
     </row>
-    <row r="10" spans="1:61">
-      <c r="A10">
-        <v>20260731</v>
-      </c>
-      <c r="B10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C10" s="3">
-        <v>19</v>
-      </c>
-      <c r="D10" s="3">
-        <v>2</v>
-      </c>
-      <c r="E10">
-        <v>4449.3999999999996</v>
-      </c>
-      <c r="F10">
-        <v>4254.08</v>
-      </c>
-      <c r="G10">
-        <v>4011.89</v>
-      </c>
-      <c r="H10" t="s">
-        <v>70</v>
-      </c>
-      <c r="I10">
-        <v>24</v>
-      </c>
-      <c r="J10">
-        <v>25</v>
-      </c>
-      <c r="K10">
-        <v>24</v>
-      </c>
-      <c r="L10">
-        <v>25</v>
-      </c>
-      <c r="M10">
-        <v>25</v>
-      </c>
-      <c r="N10">
-        <v>24</v>
-      </c>
-      <c r="O10">
-        <v>25</v>
-      </c>
-      <c r="P10">
-        <v>25</v>
-      </c>
-      <c r="Q10">
-        <v>4216.7</v>
-      </c>
-      <c r="R10">
-        <v>4250.3999999999996</v>
-      </c>
-      <c r="S10">
-        <v>4449.3999999999996</v>
-      </c>
-      <c r="T10">
-        <v>4449.2</v>
-      </c>
-      <c r="U10">
-        <v>4304</v>
-      </c>
-      <c r="V10">
-        <v>4211.6000000000004</v>
-      </c>
-      <c r="W10">
-        <v>4277.3999999999996</v>
-      </c>
-      <c r="X10">
-        <v>4379</v>
-      </c>
-      <c r="Y10">
-        <v>4449.1000000000004</v>
-      </c>
-      <c r="Z10">
-        <v>4137.5</v>
-      </c>
-      <c r="AA10">
-        <v>4449.3999999999996</v>
-      </c>
-      <c r="AB10">
-        <v>4061.2</v>
-      </c>
-      <c r="AC10">
-        <v>4295.7</v>
-      </c>
-      <c r="AD10">
-        <v>4374.5</v>
-      </c>
-      <c r="AE10">
-        <v>4219.6000000000004</v>
-      </c>
-      <c r="AF10">
-        <v>4315.6000000000004</v>
-      </c>
-      <c r="AG10">
-        <v>4254.3</v>
-      </c>
-      <c r="AH10">
-        <v>4225.6000000000004</v>
-      </c>
-      <c r="AI10">
-        <v>4361.3</v>
-      </c>
-      <c r="AJ10">
-        <v>4379</v>
-      </c>
-      <c r="AK10">
-        <v>4449.3999999999996</v>
-      </c>
-      <c r="AL10">
-        <v>4292.5</v>
-      </c>
-      <c r="AM10">
-        <v>4266.5</v>
-      </c>
-      <c r="AN10">
-        <v>4206.3999999999996</v>
-      </c>
-      <c r="AO10">
-        <v>4372.2</v>
-      </c>
-      <c r="AP10">
-        <v>4373.3</v>
-      </c>
-      <c r="AQ10">
-        <v>4176.7</v>
-      </c>
-      <c r="AR10">
-        <v>4365.7</v>
-      </c>
-      <c r="AS10">
-        <v>4346.6000000000004</v>
-      </c>
-      <c r="AT10">
-        <v>4365.1000000000004</v>
-      </c>
-      <c r="AU10">
-        <v>4295.2</v>
-      </c>
-      <c r="AV10">
-        <v>4326.5</v>
-      </c>
-      <c r="AW10">
-        <v>4341.2</v>
-      </c>
-      <c r="AX10">
-        <v>4379</v>
-      </c>
-      <c r="AY10">
-        <v>4101.7</v>
-      </c>
-      <c r="AZ10">
-        <v>4347.3</v>
-      </c>
-      <c r="BA10">
-        <v>4327.8</v>
-      </c>
-      <c r="BB10">
-        <v>4379</v>
-      </c>
-      <c r="BC10">
-        <v>4325.1000000000004</v>
-      </c>
-      <c r="BD10">
-        <v>4236.3</v>
-      </c>
-      <c r="BE10">
-        <v>4019.01</v>
-      </c>
-      <c r="BF10">
-        <v>4256.62</v>
-      </c>
-      <c r="BG10">
-        <v>1647865</v>
-      </c>
-      <c r="BH10">
-        <v>1648</v>
-      </c>
-      <c r="BI10">
-        <v>16481</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/大秘境分数行情_至暗之夜第一赛季.xlsx
+++ b/大秘境分数行情_至暗之夜第一赛季.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI10"/>
+  <dimension ref="A1:BI11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2422,6 +2422,195 @@
         <v>16482</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>20260801</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4450.8</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4254.75</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4012.72</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Butaneanzx-D邪DK,Zevokerr-D增辉,Razhäg-H奶僧</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>24</v>
+      </c>
+      <c r="J11" t="n">
+        <v>25</v>
+      </c>
+      <c r="K11" t="n">
+        <v>24</v>
+      </c>
+      <c r="L11" t="n">
+        <v>25</v>
+      </c>
+      <c r="M11" t="n">
+        <v>25</v>
+      </c>
+      <c r="N11" t="n">
+        <v>24</v>
+      </c>
+      <c r="O11" t="n">
+        <v>25</v>
+      </c>
+      <c r="P11" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R11" t="n">
+        <v>4250.4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4450.8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4450.6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4304</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4211.6</v>
+      </c>
+      <c r="W11" t="n">
+        <v>4277.4</v>
+      </c>
+      <c r="X11" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>4449.6</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4450.8</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>4061.2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>4374.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>4219.6</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>4315.9</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>4254.3</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>4375.4</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>4450.8</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>4266.5</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>4206.4</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>4377.2</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>4176.7</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>4365.7</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>4346.6</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>4326.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>4341.2</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>4101.7</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>4347.3</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>4379</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4325.1</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4247.5</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>4021.76</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>4257.49</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1652055</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1657</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>16523</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/大秘境分数行情_至暗之夜第一赛季.xlsx
+++ b/大秘境分数行情_至暗之夜第一赛季.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI11"/>
+  <dimension ref="A1:BI12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2611,6 +2611,195 @@
         <v>16523</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>20260802</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>19</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4450.8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4255.97</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4013.65</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Butaneanzx-D邪DK,Zevokerr-D增辉,Razhäg-H奶僧</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>24</v>
+      </c>
+      <c r="J12" t="n">
+        <v>25</v>
+      </c>
+      <c r="K12" t="n">
+        <v>24</v>
+      </c>
+      <c r="L12" t="n">
+        <v>25</v>
+      </c>
+      <c r="M12" t="n">
+        <v>25</v>
+      </c>
+      <c r="N12" t="n">
+        <v>24</v>
+      </c>
+      <c r="O12" t="n">
+        <v>25</v>
+      </c>
+      <c r="P12" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R12" t="n">
+        <v>4250.4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4450.8</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4450.6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4304</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4226.7</v>
+      </c>
+      <c r="W12" t="n">
+        <v>4277.4</v>
+      </c>
+      <c r="X12" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>4450.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4450.8</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>4074.4</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>4374.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>4219.8</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>4315.9</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>4375.4</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>4450.8</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>4206.4</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>4377.4</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>4176.7</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>4365.7</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>4347.8</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>4326.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>4341.2</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>4101.7</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>4347.3</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4379</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>4325.1</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4249</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>4023.91</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>4258.89</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1657191</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1658</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>16574</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/大秘境分数行情_至暗之夜第一赛季.xlsx
+++ b/大秘境分数行情_至暗之夜第一赛季.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI12"/>
+  <dimension ref="A1:BI13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2800,6 +2800,195 @@
         <v>16574</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>20260803</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>19</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4451.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4256.6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4014.77</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Titiquemonk-H奶僧,Nzangellips-D噬灭,Zacdruid-T熊T,Myzouth-D邪DK,Nikovoker-D增辉</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>24</v>
+      </c>
+      <c r="J13" t="n">
+        <v>25</v>
+      </c>
+      <c r="K13" t="n">
+        <v>24</v>
+      </c>
+      <c r="L13" t="n">
+        <v>25</v>
+      </c>
+      <c r="M13" t="n">
+        <v>25</v>
+      </c>
+      <c r="N13" t="n">
+        <v>24</v>
+      </c>
+      <c r="O13" t="n">
+        <v>25</v>
+      </c>
+      <c r="P13" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4252.9</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4451.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4451.5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4304</v>
+      </c>
+      <c r="V13" t="n">
+        <v>4226.7</v>
+      </c>
+      <c r="W13" t="n">
+        <v>4277.4</v>
+      </c>
+      <c r="X13" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>4451.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4451.5</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>4074.4</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4374.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>4219.8</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>4317.1</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>4375.4</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>4451.5</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>4206.4</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>4176.7</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4365.7</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4347.8</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4326.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4351.7</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>4347.3</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>4379</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4325.1</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4249</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4025.64</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>4260.17</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>1663040</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>1665</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>16631</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/大秘境分数行情_至暗之夜第一赛季.xlsx
+++ b/大秘境分数行情_至暗之夜第一赛季.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI13"/>
+  <dimension ref="A1:BI14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2989,6 +2989,195 @@
         <v>16631</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>20260804</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>19</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4453.8</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4257.03</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4015.96</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>24</v>
+      </c>
+      <c r="J14" t="n">
+        <v>25</v>
+      </c>
+      <c r="K14" t="n">
+        <v>24</v>
+      </c>
+      <c r="L14" t="n">
+        <v>25</v>
+      </c>
+      <c r="M14" t="n">
+        <v>25</v>
+      </c>
+      <c r="N14" t="n">
+        <v>24</v>
+      </c>
+      <c r="O14" t="n">
+        <v>25</v>
+      </c>
+      <c r="P14" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R14" t="n">
+        <v>4252.9</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4453.8</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4452.6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4304</v>
+      </c>
+      <c r="V14" t="n">
+        <v>4226.7</v>
+      </c>
+      <c r="W14" t="n">
+        <v>4277.4</v>
+      </c>
+      <c r="X14" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>4452.6</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4453.6</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>4374.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>4234</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>4317.1</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>4453.6</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>4214.9</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>4176.7</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>4365.7</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>4347.8</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>4326.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>4351.7</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>4347.3</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>4379</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4325.1</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4249</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>4026.93</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>4261.1</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>1667698</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>1668</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>16681</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/大秘境分数行情_至暗之夜第一赛季.xlsx
+++ b/大秘境分数行情_至暗之夜第一赛季.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17920" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="每日数据" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="强势阵容" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="强势阵容" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
         <v>4449.1</v>

--- a/大秘境分数行情_至暗之夜第一赛季.xlsx
+++ b/大秘境分数行情_至暗之夜第一赛季.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17920" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日数据" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="强势阵容" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="每日数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="强势阵容" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI14"/>
+  <dimension ref="A1:BI15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3178,6 +3178,195 @@
         <v>16681</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20260805</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>19</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4453.8</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4258.32</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4017.57</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>24</v>
+      </c>
+      <c r="J15" t="n">
+        <v>25</v>
+      </c>
+      <c r="K15" t="n">
+        <v>24</v>
+      </c>
+      <c r="L15" t="n">
+        <v>25</v>
+      </c>
+      <c r="M15" t="n">
+        <v>25</v>
+      </c>
+      <c r="N15" t="n">
+        <v>24</v>
+      </c>
+      <c r="O15" t="n">
+        <v>25</v>
+      </c>
+      <c r="P15" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R15" t="n">
+        <v>4252.9</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4453.8</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4452.6</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4304</v>
+      </c>
+      <c r="V15" t="n">
+        <v>4241.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>4277.4</v>
+      </c>
+      <c r="X15" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>4452.6</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4453.6</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4374.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>4234.9</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>4453.6</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>4214.9</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>4176.7</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4347.8</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4351.7</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>4359</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>4379</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4249</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4028.23</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>4262.47</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>1672799</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>1674</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>16728</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
